--- a/artfynd/A 63961-2021 artfynd.xlsx
+++ b/artfynd/A 63961-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63961-2021 artfynd.xlsx
+++ b/artfynd/A 63961-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102589785</v>
+        <v>105970851</v>
       </c>
       <c r="B2" t="n">
-        <v>106912</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223701</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig klofibbla</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crepis tectorum var. tectorum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bulsjö, Djurstugan, 265 m VSV, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516892</v>
+        <v>516919</v>
       </c>
       <c r="R2" t="n">
-        <v>6410192</v>
+        <v>6409700</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
+          <t>2023-01-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
+          <t>2023-01-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,35 +762,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>grusmark vid elskåp</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Åke Bruhn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson, Tommy Nilsson</t>
+          <t>Åke Bruhn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105970851</v>
+        <v>102589785</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,42 +788,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>223701</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig klofibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Crepis tectorum var. tectorum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Bulsjö, Djurstugan, 265 m VSV, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516919.2031532691</v>
+        <v>516892</v>
       </c>
       <c r="R3" t="n">
-        <v>6409699.952116092</v>
+        <v>6410192</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,15 +855,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>grusmark vid elskåp</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Åke Bruhn</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åke Bruhn</t>
+          <t>Anders Svenson, Tommy Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 63961-2021 artfynd.xlsx
+++ b/artfynd/A 63961-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105970851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,8 +882,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102589785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>